--- a/Assets/StreamingAssets/Chapter/Chapter0.xlsx
+++ b/Assets/StreamingAssets/Chapter/Chapter0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\shina\Assets\StreamingAssets\Chapter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05CD36AE-47F4-4F3C-B64C-BE4E63D1F675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35603810-A483-4588-B327-E6DACC511D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15390" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,54 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
-    <t>人物</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>对话</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>语音</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>背景/cg</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>背景音乐</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>转场特效</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>立绘</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>对话框头像</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>#TAG</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>选项</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>QTE</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>指令</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>UI/开幕</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -124,6 +76,42 @@
   <si>
     <t>goChapter &gt;&gt; story.序章</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>人物</t>
+  </si>
+  <si>
+    <t>对话</t>
+  </si>
+  <si>
+    <t>语音</t>
+  </si>
+  <si>
+    <t>背景/cg</t>
+  </si>
+  <si>
+    <t>背景音乐</t>
+  </si>
+  <si>
+    <t>转场特效</t>
+  </si>
+  <si>
+    <t>立绘层</t>
+  </si>
+  <si>
+    <t>对话框头像</t>
+  </si>
+  <si>
+    <t>#TAG</t>
+  </si>
+  <si>
+    <t>选项</t>
+  </si>
+  <si>
+    <t>TE. HUD层</t>
+  </si>
+  <si>
+    <t>指令</t>
   </si>
 </sst>
 </file>
@@ -583,82 +571,82 @@
   <sheetData>
     <row r="1" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B5" s="6" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="L6" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Chapter/Chapter0.xlsx
+++ b/Assets/StreamingAssets/Chapter/Chapter0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\shina\Assets\StreamingAssets\Chapter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35603810-A483-4588-B327-E6DACC511D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05CD36AE-47F4-4F3C-B64C-BE4E63D1F675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15390" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,6 +38,54 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
+    <t>人物</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>对话</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>语音</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>背景/cg</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>背景音乐</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>转场特效</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>立绘</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>对话框头像</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>#TAG</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>选项</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>QTE</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>指令</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>UI/开幕</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -76,42 +124,6 @@
   <si>
     <t>goChapter &gt;&gt; story.序章</t>
     <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>人物</t>
-  </si>
-  <si>
-    <t>对话</t>
-  </si>
-  <si>
-    <t>语音</t>
-  </si>
-  <si>
-    <t>背景/cg</t>
-  </si>
-  <si>
-    <t>背景音乐</t>
-  </si>
-  <si>
-    <t>转场特效</t>
-  </si>
-  <si>
-    <t>立绘层</t>
-  </si>
-  <si>
-    <t>对话框头像</t>
-  </si>
-  <si>
-    <t>#TAG</t>
-  </si>
-  <si>
-    <t>选项</t>
-  </si>
-  <si>
-    <t>TE. HUD层</t>
-  </si>
-  <si>
-    <t>指令</t>
   </si>
 </sst>
 </file>
@@ -571,82 +583,82 @@
   <sheetData>
     <row r="1" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B5" s="6" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="L6" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
